--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="461">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -744,6 +744,15 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R260-HL7RoleClass/FHIR/TRE-R260-HL7RoleClass"/&gt;
+    &lt;code value="CON"/&gt;
+    &lt;display value="Informateur"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
   </si>
   <si>
@@ -867,9 +876,6 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>CON</t>
-  </si>
-  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -892,9 +898,6 @@
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Informateur</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -4395,7 +4398,7 @@
         <v>76</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>76</v>
@@ -4414,7 +4417,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4458,10 +4461,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4567,10 +4570,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4678,10 +4681,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4707,16 +4710,16 @@
         <v>143</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4765,7 +4768,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4780,21 +4783,21 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4900,10 +4903,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5011,10 +5014,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5040,16 +5043,16 @@
         <v>127</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5059,7 +5062,7 @@
         <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>76</v>
@@ -5098,7 +5101,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5113,21 +5116,21 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5153,13 +5156,13 @@
         <v>99</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5209,7 +5212,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5224,21 +5227,21 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5264,14 +5267,14 @@
         <v>165</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5281,7 +5284,7 @@
         <v>76</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>76</v>
@@ -5392,46 +5395,46 @@
         <v>76</v>
       </c>
       <c r="S33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5446,21 +5449,21 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5486,16 +5489,16 @@
         <v>206</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5544,7 +5547,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5559,21 +5562,21 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5599,16 +5602,16 @@
         <v>99</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5657,7 +5660,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5672,24 +5675,24 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>221</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
@@ -5714,7 +5717,7 @@
         <v>222</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>224</v>
@@ -5746,11 +5749,11 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5794,10 +5797,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5903,10 +5906,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6014,10 +6017,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6043,16 +6046,16 @@
         <v>143</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6101,7 +6104,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6116,21 +6119,21 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6236,10 +6239,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6347,10 +6350,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6376,16 +6379,16 @@
         <v>127</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6395,7 +6398,7 @@
         <v>76</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>76</v>
@@ -6434,7 +6437,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6449,21 +6452,21 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6489,13 +6492,13 @@
         <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6545,7 +6548,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6560,21 +6563,21 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6600,14 +6603,14 @@
         <v>165</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6682,7 +6685,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>280</v>
@@ -6767,7 +6770,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6782,21 +6785,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6822,16 +6825,16 @@
         <v>206</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6880,7 +6883,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6895,21 +6898,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6935,16 +6938,16 @@
         <v>99</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -6993,7 +6996,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7008,21 +7011,21 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7045,19 +7048,19 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7106,7 +7109,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7115,27 +7118,27 @@
         <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7241,10 +7244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7352,13 +7355,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
@@ -7380,13 +7383,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7463,10 +7466,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7492,16 +7495,16 @@
         <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7526,29 +7529,29 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7563,21 +7566,21 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7603,16 +7606,16 @@
         <v>99</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7661,7 +7664,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7676,25 +7679,25 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7716,13 +7719,13 @@
         <v>99</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7772,7 +7775,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7787,25 +7790,25 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7827,13 +7830,13 @@
         <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7883,7 +7886,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7898,21 +7901,21 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7938,10 +7941,10 @@
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7968,29 +7971,29 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8005,21 +8008,21 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8045,10 +8048,10 @@
         <v>99</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8075,29 +8078,29 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8112,21 +8115,21 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8149,17 +8152,17 @@
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8208,7 +8211,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8223,21 +8226,21 @@
         <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8260,19 +8263,19 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8321,7 +8324,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8330,27 +8333,27 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AK59" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AK59" t="s" s="2">
+      <c r="AL59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8376,14 +8379,14 @@
         <v>165</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8408,14 +8411,14 @@
         <v>76</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
       </c>
@@ -8432,7 +8435,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8447,21 +8450,21 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8484,13 +8487,13 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8541,7 +8544,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8556,7 +8559,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8567,10 +8570,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8593,19 +8596,19 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>76</v>
@@ -8654,7 +8657,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8663,27 +8666,27 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8706,17 +8709,17 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8765,7 +8768,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8780,21 +8783,21 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8817,13 +8820,13 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8874,7 +8877,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8889,10 +8892,10 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8900,10 +8903,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8926,19 +8929,19 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8987,7 +8990,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9002,7 +9005,7 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -9013,10 +9016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9122,10 +9125,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9233,14 +9236,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9262,10 +9265,10 @@
         <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>109</v>
@@ -9320,7 +9323,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9346,10 +9349,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9375,16 +9378,16 @@
         <v>222</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9433,7 +9436,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>85</v>
@@ -9448,7 +9451,7 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9459,10 +9462,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9488,16 +9491,16 @@
         <v>206</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9546,7 +9549,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9561,7 +9564,7 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/main/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
